--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/搜打撤_刷怪波次配置表_SearchExtract_SearchExtractWaveSpawnConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/搜打撤_刷怪波次配置表_SearchExtract_SearchExtractWaveSpawnConfig.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="36">
   <si>
     <t>玩法配置ID</t>
   </si>
@@ -154,6 +154,15 @@
   </si>
   <si>
     <t>SP_04</t>
+  </si>
+  <si>
+    <t>SearchExtract_02</t>
+  </si>
+  <si>
+    <t>SearchExtract_03</t>
+  </si>
+  <si>
+    <t>SearchExtract_04</t>
   </si>
 </sst>
 </file>
@@ -1130,8 +1139,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
     <col min="2" max="2" width="14.375" customWidth="1"/>
@@ -1244,10 +1253,10 @@
         <v>5</v>
       </c>
       <c r="E4" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>28</v>
@@ -1256,7 +1265,7 @@
         <v>29</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1273,10 +1282,10 @@
         <v>10</v>
       </c>
       <c r="E5" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>30</v>
@@ -1285,7 +1294,7 @@
         <v>29</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1299,13 +1308,13 @@
         <v>3</v>
       </c>
       <c r="D6" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
@@ -1314,7 +1323,7 @@
         <v>29</v>
       </c>
       <c r="I6" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1328,13 +1337,13 @@
         <v>4</v>
       </c>
       <c r="D7" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>32</v>
@@ -1343,11 +1352,356 @@
         <v>29</v>
       </c>
       <c r="I7" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>25</v>
+      </c>
+      <c r="F8" s="2">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2">
+        <v>25</v>
+      </c>
+      <c r="F9" s="2">
+        <v>3</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>15</v>
+      </c>
+      <c r="E10" s="2">
+        <v>25</v>
+      </c>
+      <c r="F10" s="2">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="F8" s="2"/>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2">
+        <v>20</v>
+      </c>
+      <c r="E11" s="2">
+        <v>25</v>
+      </c>
+      <c r="F11" s="2">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2">
+        <v>25</v>
+      </c>
+      <c r="F12" s="2">
+        <v>4</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2">
+        <v>25</v>
+      </c>
+      <c r="F13" s="2">
+        <v>4</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2">
+        <v>25</v>
+      </c>
+      <c r="F14" s="2">
+        <v>4</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2">
+        <v>4</v>
+      </c>
+      <c r="D15" s="2">
+        <v>20</v>
+      </c>
+      <c r="E15" s="2">
+        <v>25</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2">
+        <v>5</v>
+      </c>
+      <c r="E16" s="2">
+        <v>25</v>
+      </c>
+      <c r="F16" s="2">
+        <v>4</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2">
+        <v>25</v>
+      </c>
+      <c r="F17" s="2">
+        <v>4</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2">
+        <v>15</v>
+      </c>
+      <c r="E18" s="2">
+        <v>25</v>
+      </c>
+      <c r="F18" s="2">
+        <v>4</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2">
+        <v>4</v>
+      </c>
+      <c r="D19" s="2">
+        <v>20</v>
+      </c>
+      <c r="E19" s="2">
+        <v>25</v>
+      </c>
+      <c r="F19" s="2">
+        <v>4</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="2">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/搜打撤_刷怪波次配置表_SearchExtract_SearchExtractWaveSpawnConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/搜打撤_刷怪波次配置表_SearchExtract_SearchExtractWaveSpawnConfig.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="40">
   <si>
     <t>玩法配置ID</t>
   </si>
@@ -157,6 +157,18 @@
   </si>
   <si>
     <t>SearchExtract_02</t>
+  </si>
+  <si>
+    <t>SP_11</t>
+  </si>
+  <si>
+    <t>SP_12</t>
+  </si>
+  <si>
+    <t>SP_13</t>
+  </si>
+  <si>
+    <t>SP_14</t>
   </si>
   <si>
     <t>SearchExtract_03</t>
@@ -787,9 +799,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1139,7 +1154,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
@@ -1473,10 +1488,10 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -1488,24 +1503,24 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I12" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
@@ -1517,24 +1532,24 @@
         <v>25</v>
       </c>
       <c r="F13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I13" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2</v>
       </c>
       <c r="C14" s="2">
         <v>3</v>
@@ -1546,10 +1561,10 @@
         <v>25</v>
       </c>
       <c r="F14" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>29</v>
@@ -1560,10 +1575,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="2">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2</v>
       </c>
       <c r="C15" s="2">
         <v>4</v>
@@ -1575,10 +1590,10 @@
         <v>25</v>
       </c>
       <c r="F15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>29</v>
@@ -1589,7 +1604,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2">
         <v>1</v>
@@ -1613,12 +1628,12 @@
         <v>29</v>
       </c>
       <c r="I16" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2">
         <v>1</v>
@@ -1642,12 +1657,12 @@
         <v>29</v>
       </c>
       <c r="I17" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -1671,12 +1686,12 @@
         <v>29</v>
       </c>
       <c r="I18" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -1700,6 +1715,122 @@
         <v>29</v>
       </c>
       <c r="I19" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2">
+        <v>5</v>
+      </c>
+      <c r="E20" s="2">
+        <v>25</v>
+      </c>
+      <c r="F20" s="2">
+        <v>4</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2">
+        <v>2</v>
+      </c>
+      <c r="D21" s="2">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2">
+        <v>25</v>
+      </c>
+      <c r="F21" s="2">
+        <v>4</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
+        <v>15</v>
+      </c>
+      <c r="E22" s="2">
+        <v>25</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2">
+        <v>4</v>
+      </c>
+      <c r="D23" s="2">
+        <v>20</v>
+      </c>
+      <c r="E23" s="2">
+        <v>25</v>
+      </c>
+      <c r="F23" s="2">
+        <v>4</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" s="2">
         <v>10</v>
       </c>
     </row>
